--- a/output/통합_클라우드보안위협_매트릭스_v5.xlsx
+++ b/output/통합_클라우드보안위협_매트릭스_v5.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11대 위협 연계(기법 단위) — 원문 미수록, 연계 ID만</t>
+          <t>11대 위협 연계(기법 단위, 하위기법 지정 시 우선) — 원문 미수록, 연계 ID만</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11대 위협별 연계 세부위협 수·사고 수와 보고서 사례 목록</t>
+          <t>11대 위협별 연계 세부위협·사고 수와 연계 기준(SI-02·SI-08 교차 위협, SI-06은 AI 매트릭스 UT 연계)</t>
         </is>
       </c>
     </row>
@@ -23422,7 +23422,7 @@
           <t>■ 클라우드 관점
 - 유형: 컴퓨트로 암호화폐 채굴(EC2·ECS·EKS·WorkSpaces, AWS TTC T1496.A006·A008·A010), SES로 스팸·발송(A001), Bedrock 등 관리형 LLM 무단 호출(LLMjacking, A007)
 - 진입: 인증 없는 노출 서비스(Ray·Open WebUI·LiteLLM-Proxy), 약인증 SSH, 공개 버킷 자격증명 — 침해 후 할당량 상향(CTC-DI-05.5)으로 규모 확대
-- CSA 2026은 LLMjacking 등 AI 자원 악용 맥락에서 SI-06으로 연계하나, 본 기법의 본질은 자원·과금 악용
+- CSA 2026: 영향 기법이라 상위기법은 이슈 미연계 — 침투 경로는 사고마다 취약점 악용·노출 서비스·자격증명 계열(SI-11·SI-05·SI-01 성격)로 갈림. SI-06(AI 시스템 침해)은 LLMjacking을 다루는 하위기법(CTC-IM-09.4)에만 연계
 - 사고 DB에서 가장 많이 매핑된 기법(127건), 하위기법(CTC-IM-09.1~09.4)으로 세분
 ■ 실제 사례
 - [실제 사고] Operation Bizarre Bazaar(2026-01): 노출 LLM·MCP 인프라를 노린 상업화된 LLMjacking 캠페인 (사고DB INC-0589)
@@ -23461,11 +23461,7 @@
           <t>사용자 입력</t>
         </is>
       </c>
-      <c r="N152" s="17" t="inlineStr">
-        <is>
-          <t>SI-06 AI 시스템 침해</t>
-        </is>
-      </c>
+      <c r="N152" s="17" t="inlineStr"/>
       <c r="O152" s="17" t="inlineStr"/>
       <c r="P152" s="17" t="inlineStr">
         <is>
@@ -23622,11 +23618,7 @@
           <t>사용자 입력</t>
         </is>
       </c>
-      <c r="N153" s="17" t="inlineStr">
-        <is>
-          <t>SI-06 AI 시스템 침해</t>
-        </is>
-      </c>
+      <c r="N153" s="17" t="inlineStr"/>
       <c r="O153" s="17" t="inlineStr"/>
       <c r="P153" s="17" t="inlineStr">
         <is>
@@ -23765,11 +23757,7 @@
           <t>사용자 입력</t>
         </is>
       </c>
-      <c r="N154" s="17" t="inlineStr">
-        <is>
-          <t>SI-06 AI 시스템 침해</t>
-        </is>
-      </c>
+      <c r="N154" s="17" t="inlineStr"/>
       <c r="O154" s="17" t="inlineStr"/>
       <c r="P154" s="17" t="inlineStr"/>
       <c r="Q154" s="17" t="inlineStr"/>
@@ -23866,7 +23854,7 @@
           <t>■ 클라우드 관점
 - 공개 웹 폼(OTP·계정 확인)이 뒤에서 호출하는 Amazon SNS·Cognito·Twilio를 악용 — cognito:SignUp·ForgotPassword·sns:Publish로 SMS 트래픽 유발(AWS TTC T1496.003)
 - 공격자가 확보한 고요율 번호로 발송을 유도해 수익을 얻고, 피해자에게 SMS 과금 급증·채널 과부하 발생
-- 상위기법(CTC-IM-09.0)의 메시징 변형 — 폼 레이트 제한·CAPTCHA·발송 상한이 방어 핵심
+- 상위기법(CTC-IM-09.0)의 메시징 변형 — 폼 레이트 제한·CAPTCHA·발송 상한이 방어 핵심(CSA 2026 SI-04 '레이트 제한 없는 API의 자원 고갈'과 연계)
 ■ 실제 사례
 - 공개 사고 미확인 — 사고 DB·ATT&amp;CK 클라우드 사례에 매핑된 건은 없음(벤더·ATT&amp;CK 문서화 수준)</t>
         </is>
@@ -23904,7 +23892,7 @@
       </c>
       <c r="N155" s="17" t="inlineStr">
         <is>
-          <t>SI-06 AI 시스템 침해</t>
+          <t>SI-04 안전하지 않은 인터페이스·API</t>
         </is>
       </c>
       <c r="O155" s="17" t="inlineStr"/>
@@ -24007,7 +23995,7 @@
           <t>■ 클라우드 관점
 - 메일·메시징 서비스(SES·SNS·SendGrid·Twilio)로 대량 스팸·피싱(T1496.A001), 관리형 LLM(Amazon Bedrock) 무단 호출로 LLMjacking(A007)
 - 피해자가 이미 쓰는 서비스를 악용하거나, 플랫폼 일부인 서비스를 공격자가 먼저 활성화 — 과금 급증·할당량 소진·가용성 저하
-- AI 매트릭스 UT-30.2(과금 폭탄)와 연계되는 상위기법(CTC-IM-09.0)의 SaaS 변형
+- 상위기법(CTC-IM-09.0)의 SaaS 변형 — LLMjacking은 AI 매트릭스 UT-30.2(과금 폭탄)·CSA 2026 SI-06(AI 시스템 침해)과 연계
 ■ 실제 사례
 - [실제 사고] SES 샌드박스 해제 악용(2025-09): 탈취 자격증명으로 지원 요청을 통해 SES 샌드박스를 풀고 피싱 발송에 악용 (사고DB INC-0554)
 - [실제 사고] LiteLLM-Proxy 노출 침해(2026-06): 약인증 SSH로 침투해 Bedrock InvokeModel을 시도, LLMjacking 가능성 확인 (사고DB INC-0635)</t>
@@ -24046,7 +24034,7 @@
       </c>
       <c r="N156" s="17" t="inlineStr">
         <is>
-          <t>SI-06 AI 시스템 침해</t>
+          <t>SI-01 부적절한 IAM · SI-06 AI 시스템 침해</t>
         </is>
       </c>
       <c r="O156" s="17" t="inlineStr">
@@ -35956,11 +35944,7 @@
           <t>혼합</t>
         </is>
       </c>
-      <c r="H150" s="17" t="inlineStr">
-        <is>
-          <t>SI-06 AI 시스템 침해</t>
-        </is>
-      </c>
+      <c r="H150" s="17" t="inlineStr"/>
       <c r="I150" s="19" t="inlineStr">
         <is>
           <t>상</t>
@@ -36035,11 +36019,7 @@
           <t>혼합</t>
         </is>
       </c>
-      <c r="H151" s="17" t="inlineStr">
-        <is>
-          <t>SI-06 AI 시스템 침해</t>
-        </is>
-      </c>
+      <c r="H151" s="17" t="inlineStr"/>
       <c r="I151" s="19" t="inlineStr">
         <is>
           <t>중</t>
@@ -36114,11 +36094,7 @@
           <t>혼합</t>
         </is>
       </c>
-      <c r="H152" s="17" t="inlineStr">
-        <is>
-          <t>SI-06 AI 시스템 침해</t>
-        </is>
-      </c>
+      <c r="H152" s="17" t="inlineStr"/>
       <c r="I152" s="19" t="inlineStr">
         <is>
           <t>하</t>
@@ -36195,7 +36171,7 @@
       </c>
       <c r="H153" s="17" t="inlineStr">
         <is>
-          <t>SI-06 AI 시스템 침해</t>
+          <t>SI-04 안전하지 않은 인터페이스·API</t>
         </is>
       </c>
       <c r="I153" s="19" t="inlineStr">
@@ -36274,7 +36250,7 @@
       </c>
       <c r="H154" s="17" t="inlineStr">
         <is>
-          <t>SI-06 AI 시스템 침해</t>
+          <t>SI-01 부적절한 IAM · SI-06 AI 시스템 침해</t>
         </is>
       </c>
       <c r="I154" s="19" t="inlineStr">
@@ -37377,15 +37353,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37411,12 +37389,22 @@
       </c>
       <c r="E1" s="16" t="inlineStr">
         <is>
-          <t>연계 실제 사고 수</t>
+          <t>연계 사고 수</t>
         </is>
       </c>
       <c r="F1" s="16" t="inlineStr">
         <is>
-          <t>연계 세부위협(위험 높음 이상)</t>
+          <t>그중 실제 사고</t>
+        </is>
+      </c>
+      <c r="G1" s="16" t="inlineStr">
+        <is>
+          <t>연계 기준</t>
+        </is>
+      </c>
+      <c r="H1" s="16" t="inlineStr">
+        <is>
+          <t>연계 세부위협(위험 높음 이상, 없으면 전체)</t>
         </is>
       </c>
     </row>
@@ -37431,18 +37419,60 @@
           <t>부적절한 IAM</t>
         </is>
       </c>
-      <c r="C2" s="17" t="n">
-        <v>52</v>
-      </c>
-      <c r="D2" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="E2" s="17" t="n">
+      <c r="C2" s="19" t="n">
+        <v>53</v>
+      </c>
+      <c r="D2" s="19" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="F2" s="17" t="inlineStr">
-        <is>
-          <t>CTC-CA-02.1 Password Guessing, CTC-CA-02.2 Password Spraying, CTC-CA-03.1 Cloud Secrets Management Stores, CTC-CA-04.2 SAML Tokens, CTC-CA-05.1 Multi-Factor Authentication, CTC-CA-05.2 Hybrid Identity, CTC-CA-05.3 Conditional Access Policies, CTC-CA-07 Steal Application Access Token, CTC-CA-08 Steal or Forge Authentication Certificates, CTC-CA-09 Steal Web Session Cookie, CTC-DI-03.0 Domain or Tenant Policy Modification (일반·상위기법), CTC-DI-03.1 Trust Modification, CTC-DI-04.1 Multi-Factor Authentication, CTC-IA-03.0 Phishing (일반·상위기법), CTC-IA-03.1 Spearphishing Link, CTC-IA-06.2 Cloud Accounts, CTC-LM-06.1 Application Access Token, CTC-LM-06.2 Web Session Cookie, CTC-PE-01.1 Additional Cloud Credentials, CTC-PE-01.2 Additional Email Delegate Permissions, CTC-PE-01.3 Additional Cloud Roles, CTC-PE-01.5 Device Registration, CTC-PE-03.1 Cloud Account, CTC-PE-08.1 Multi-Factor Authentication, CTC-PE-11.2 Cloud Accounts, CTC-PV-01.1 Temporary Elevated Cloud Access, CTC-PV-02.1 Additional Cloud Credentials, CTC-PV-02.2 Additional Email Delegate Permissions, CTC-PV-02.3 Additional Cloud Roles, CTC-PV-02.5 Device Registration, CTC-PV-04.0 Domain or Tenant Policy Modification (일반·상위기법), CTC-PV-04.1 Trust Modification, CTC-PV-08.2 Cloud Accounts, CTC-ST-06.2 Cloud Accounts</t>
+      <c r="F2" s="19" t="n">
+        <v>93</v>
+      </c>
+      <c r="G2" s="17" t="inlineStr">
+        <is>
+          <t>기법 주제 기준 1차 매핑(scripts/taxonomy_rules.py의 CSA_MAP)</t>
+        </is>
+      </c>
+      <c r="H2" s="17" t="inlineStr">
+        <is>
+          <t>CTC-CA-02.1 Password Guessing (높음)
+CTC-CA-02.2 Password Spraying (매우 높음)
+CTC-CA-03.1 Cloud Secrets Management Stores (높음)
+CTC-CA-04.2 SAML Tokens (매우 높음)
+CTC-CA-05.1 Multi-Factor Authentication (매우 높음)
+CTC-CA-05.2 Hybrid Identity (높음)
+CTC-CA-05.3 Conditional Access Policies (높음)
+CTC-CA-07 Steal Application Access Token (매우 높음)
+CTC-CA-08 Steal or Forge Authentication Certificates (높음)
+CTC-CA-09 Steal Web Session Cookie (높음)
+CTC-DI-03.0 Domain or Tenant Policy Modification (일반·상위기법) (높음)
+CTC-DI-03.1 Trust Modification (높음)
+CTC-DI-04.1 Multi-Factor Authentication (높음)
+CTC-IA-03.0 Phishing (일반·상위기법) (매우 높음)
+CTC-IA-03.1 Spearphishing Link (높음)
+CTC-IA-06.2 Cloud Accounts (매우 높음)
+CTC-IM-09.4 Cloud Service Hijacking (높음)
+CTC-LM-06.1 Application Access Token (높음)
+CTC-LM-06.2 Web Session Cookie (높음)
+CTC-PE-01.1 Additional Cloud Credentials (높음)
+CTC-PE-01.2 Additional Email Delegate Permissions (높음)
+CTC-PE-01.3 Additional Cloud Roles (높음)
+CTC-PE-01.5 Device Registration (높음)
+CTC-PE-03.1 Cloud Account (높음)
+CTC-PE-08.1 Multi-Factor Authentication (높음)
+CTC-PE-11.2 Cloud Accounts (매우 높음)
+CTC-PV-01.1 Temporary Elevated Cloud Access (높음)
+CTC-PV-02.1 Additional Cloud Credentials (높음)
+CTC-PV-02.2 Additional Email Delegate Permissions (높음)
+CTC-PV-02.3 Additional Cloud Roles (높음)
+CTC-PV-02.5 Device Registration (높음)
+CTC-PV-04.0 Domain or Tenant Policy Modification (일반·상위기법) (높음)
+CTC-PV-04.1 Trust Modification (높음)
+CTC-PV-08.2 Cloud Accounts (매우 높음)
+CTC-ST-06.2 Cloud Accounts (매우 높음)</t>
         </is>
       </c>
     </row>
@@ -37457,20 +37487,24 @@
           <t>AI를 이용한 공격</t>
         </is>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>교차 위협(특정 기법 비종속) — 보고서 사례로만 연계</t>
-        </is>
-      </c>
+      <c r="F3" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>기법 비종속 교차 위협(공격자가 AI로 기존 기법을 가속·자동화) — 개별 세부위협 미연계, 보고서 사례로만 참조</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
@@ -37483,18 +37517,28 @@
           <t>안전하지 않은 서드파티 리소스</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>CTC-CA-07 Steal Application Access Token, CTC-IA-04.1 Compromise Software Supply Chain, CTC-IA-05 Trusted Relationship</t>
+      <c r="F4" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>기법 주제 기준 1차 매핑(scripts/taxonomy_rules.py의 CSA_MAP)</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>CTC-CA-07 Steal Application Access Token (매우 높음)
+CTC-IA-04.1 Compromise Software Supply Chain (높음)
+CTC-IA-05 Trusted Relationship (높음)</t>
         </is>
       </c>
     </row>
@@ -37509,18 +37553,27 @@
           <t>안전하지 않은 인터페이스·API</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D5" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="17" t="n">
+      <c r="C5" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>CTC-IA-01 Exploit Public-Facing Application</t>
+      <c r="F5" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>기법 주제 기준 1차 매핑(scripts/taxonomy_rules.py의 CSA_MAP)</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>CTC-IA-01 Exploit Public-Facing Application (매우 높음)
+CTC-IM-09.3 SMS Pumping (높음)</t>
         </is>
       </c>
     </row>
@@ -37535,18 +37588,32 @@
           <t>잘못된 구성·변경통제 미흡</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>CTC-CO-03 Data from Cloud Storage, CTC-DI-03.0 Domain or Tenant Policy Modification (일반·상위기법), CTC-DI-03.1 Trust Modification, CTC-DI-06 Modify Cloud Resource Hierarchy, CTC-EF-03 Transfer Data to Cloud Account, CTC-PV-04.0 Domain or Tenant Policy Modification (일반·상위기법), CTC-PV-04.1 Trust Modification</t>
+      <c r="F6" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>기법 주제 기준 1차 매핑(scripts/taxonomy_rules.py의 CSA_MAP)</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>CTC-CO-03 Data from Cloud Storage (매우 높음)
+CTC-DI-03.0 Domain or Tenant Policy Modification (일반·상위기법) (높음)
+CTC-DI-03.1 Trust Modification (높음)
+CTC-DI-06 Modify Cloud Resource Hierarchy (높음)
+CTC-EF-03 Transfer Data to Cloud Account (높음)
+CTC-PV-04.0 Domain or Tenant Policy Modification (일반·상위기법) (높음)
+CTC-PV-04.1 Trust Modification (높음)</t>
         </is>
       </c>
     </row>
@@ -37561,18 +37628,26 @@
           <t>AI 시스템 침해</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>127</v>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>CTC-IM-09.0 Resource Hijacking (일반·상위기법), CTC-IM-09.1 Compute Hijacking, CTC-IM-09.3 SMS Pumping, CTC-IM-09.4 Cloud Service Hijacking</t>
+      <c r="C7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>AI 시스템 자체 위협(프롬프트 주입·모델/데이터 오염·에이전트 악용)은 통합 AI 매트릭스 v3.2(UT) 영역 — 본 매트릭스는 관리형 AI 자원 악용(LLMjacking, T1496.004)만 연계</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>CTC-IM-09.4 Cloud Service Hijacking (높음)</t>
         </is>
       </c>
     </row>
@@ -37587,18 +37662,30 @@
           <t>APT</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>CTC-IA-05 Trusted Relationship, CTC-IA-06.2 Cloud Accounts, CTC-PE-11.2 Cloud Accounts, CTC-PV-08.2 Cloud Accounts, CTC-ST-06.2 Cloud Accounts</t>
+      <c r="F8" s="19" t="n">
+        <v>41</v>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>기법 주제 기준 1차 매핑(scripts/taxonomy_rules.py의 CSA_MAP)</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>CTC-IA-05 Trusted Relationship (높음)
+CTC-IA-06.2 Cloud Accounts (매우 높음)
+CTC-PE-11.2 Cloud Accounts (매우 높음)
+CTC-PV-08.2 Cloud Accounts (매우 높음)
+CTC-ST-06.2 Cloud Accounts (매우 높음)</t>
         </is>
       </c>
     </row>
@@ -37613,20 +37700,24 @@
           <t>클라우드 보안전략·거버넌스 부재</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>교차 위협(특정 기법 비종속) — 보고서 사례로만 연계</t>
-        </is>
-      </c>
+      <c r="F9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>비기술 거버넌스 위협 — 개별 세부위협 미연계, 보고서 사례로만 참조</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
@@ -37639,18 +37730,38 @@
           <t>안전하지 않은 소프트웨어 개발</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>CTC-CA-10.0 Unsecured Credentials (일반·상위기법), CTC-CA-10.1 Credentials In Files, CTC-CA-10.2 Cloud Instance Metadata API, CTC-CA-10.3 Container API, CTC-CA-10.4 Chat Messages, CTC-CO-04.0 Data from Information Repositories (일반·상위기법), CTC-CO-04.1 Confluence, CTC-CO-04.2 Sharepoint, CTC-CO-04.3 Code Repositories, CTC-CO-04.4 Customer Relationship Management Software, CTC-CO-04.5 Messaging Applications, CTC-CO-04.6 Databases, CTC-IA-04.1 Compromise Software Supply Chain</t>
+      <c r="F10" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>기법 주제 기준 1차 매핑(scripts/taxonomy_rules.py의 CSA_MAP)</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>CTC-CA-10.0 Unsecured Credentials (일반·상위기법) (높음)
+CTC-CA-10.1 Credentials In Files (높음)
+CTC-CA-10.2 Cloud Instance Metadata API (매우 높음)
+CTC-CA-10.3 Container API (높음)
+CTC-CA-10.4 Chat Messages (높음)
+CTC-CO-04.0 Data from Information Repositories (일반·상위기법) (매우 높음)
+CTC-CO-04.1 Confluence (높음)
+CTC-CO-04.2 Sharepoint (높음)
+CTC-CO-04.3 Code Repositories (높음)
+CTC-CO-04.4 Customer Relationship Management Software (높음)
+CTC-CO-04.5 Messaging Applications (높음)
+CTC-CO-04.6 Databases (높음)
+CTC-IA-04.1 Compromise Software Supply Chain (높음)</t>
         </is>
       </c>
     </row>
@@ -37665,18 +37776,42 @@
           <t>의도치 않은 클라우드 데이터 노출</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="19" t="n">
         <v>32</v>
       </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>CTC-CA-03.1 Cloud Secrets Management Stores, CTC-CA-10.0 Unsecured Credentials (일반·상위기법), CTC-CA-10.1 Credentials In Files, CTC-CA-10.2 Cloud Instance Metadata API, CTC-CA-10.3 Container API, CTC-CA-10.4 Chat Messages, CTC-CO-03 Data from Cloud Storage, CTC-CO-04.0 Data from Information Repositories (일반·상위기법), CTC-CO-04.1 Confluence, CTC-CO-04.2 Sharepoint, CTC-CO-04.3 Code Repositories, CTC-CO-04.4 Customer Relationship Management Software, CTC-CO-04.5 Messaging Applications, CTC-CO-04.6 Databases, CTC-EF-02.0 Exfiltration Over Web Service (일반·상위기법), CTC-EF-02.1 Exfiltration Over Webhook, CTC-EF-03 Transfer Data to Cloud Account</t>
+      <c r="F11" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>기법 주제 기준 1차 매핑(scripts/taxonomy_rules.py의 CSA_MAP)</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>CTC-CA-03.1 Cloud Secrets Management Stores (높음)
+CTC-CA-10.0 Unsecured Credentials (일반·상위기법) (높음)
+CTC-CA-10.1 Credentials In Files (높음)
+CTC-CA-10.2 Cloud Instance Metadata API (매우 높음)
+CTC-CA-10.3 Container API (높음)
+CTC-CA-10.4 Chat Messages (높음)
+CTC-CO-03 Data from Cloud Storage (매우 높음)
+CTC-CO-04.0 Data from Information Repositories (일반·상위기법) (매우 높음)
+CTC-CO-04.1 Confluence (높음)
+CTC-CO-04.2 Sharepoint (높음)
+CTC-CO-04.3 Code Repositories (높음)
+CTC-CO-04.4 Customer Relationship Management Software (높음)
+CTC-CO-04.5 Messaging Applications (높음)
+CTC-CO-04.6 Databases (높음)
+CTC-EF-02.0 Exfiltration Over Web Service (일반·상위기법) (높음)
+CTC-EF-02.1 Exfiltration Over Webhook (높음)
+CTC-EF-03 Transfer Data to Cloud Account (높음)</t>
         </is>
       </c>
     </row>
@@ -37691,18 +37826,26 @@
           <t>시스템 취약점</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>CTC-IA-01 Exploit Public-Facing Application</t>
+      <c r="F12" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>기법 주제 기준 1차 매핑(scripts/taxonomy_rules.py의 CSA_MAP)</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>CTC-IA-01 Exploit Public-Facing Application (매우 높음)</t>
         </is>
       </c>
     </row>
